--- a/sheets/조재수대금교본/검수/메기의 추억.xlsx
+++ b/sheets/조재수대금교본/검수/메기의 추억.xlsx
@@ -2806,8 +2806,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="I4" s="23"/>
@@ -2870,8 +2869,7 @@
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2887,11 +2885,7 @@
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -2952,8 +2946,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -3028,11 +3021,7 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -3093,14 +3082,13 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㅂ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3118,8 +3106,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -3171,8 +3158,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無ㅂ
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="G14" s="24"/>

--- a/sheets/조재수대금교본/검수/메기의 추억.xlsx
+++ b/sheets/조재수대금교본/검수/메기의 추억.xlsx
@@ -3088,7 +3088,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢ㅂ</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3158,7 +3158,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無ㅂ</t>
         </is>
       </c>
       <c r="G14" s="24"/>

--- a/sheets/조재수대금교본/검수/메기의 추억.xlsx
+++ b/sheets/조재수대금교본/검수/메기의 추억.xlsx
@@ -2703,24 +2703,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="43.48" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="64.57" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="64.57" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="64.57" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="64.57" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="64.57" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="64.57" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="64.57" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="64.57" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="64.57" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="64.57" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="64.57" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="64.57" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -3187,6 +3187,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="92"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>